--- a/Luban/Data/#ltext.xlsx
+++ b/Luban/Data/#ltext.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,406 +774,440 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>UI.Room.Info</t>
+          <t>UI.Lobby.ListFailed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>房间 {0}</t>
+          <t>房间列表加载失败，请重试</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Room {0}</t>
+          <t>Failed to load rooms, please retry</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>UI.Room.Waiting</t>
+          <t>UI.Room.Info</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>等待玩家 {0}/{1}</t>
+          <t>房间 {0}</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Waiting for players {0}/{1}</t>
+          <t>Room {0}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>UI.Room.PlayerState.Online</t>
+          <t>UI.Room.Waiting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>等待玩家 {0}/{1}</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Waiting for players {0}/{1}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>UI.Room.PlayerState.Connecting</t>
+          <t>UI.Room.PlayerState.Online</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>连接中</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Connecting</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>UI.Room.StartMatch</t>
+          <t>UI.Room.PlayerState.Connecting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>开始对局</t>
+          <t>连接中</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Start Match</t>
+          <t>Connecting</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>UI.Room.StartDenied</t>
+          <t>UI.Room.StartMatch</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>开局被拒：{0}</t>
+          <t>开始对局</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Start denied: {0}</t>
+          <t>Start Match</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>UI.Result.Kills</t>
+          <t>UI.Room.StartDenied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>击杀 {0}</t>
+          <t>开局被拒：{0}</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kills {0}</t>
+          <t>Start denied: {0}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>UI.Result.Deaths</t>
+          <t>UI.Result.Kills</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>死亡 {0}</t>
+          <t>击杀 {0}</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Deaths {0}</t>
+          <t>Kills {0}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>UI.Result.Score</t>
+          <t>UI.Result.Deaths</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>比分 {0}</t>
+          <t>死亡 {0}</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Score {0}</t>
+          <t>Deaths {0}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.KillLimit</t>
+          <t>UI.Result.Score</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>击杀达成</t>
+          <t>比分 {0}</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Kill limit reached</t>
+          <t>Score {0}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.TimeLimit</t>
+          <t>UI.Result.Rank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>时间到</t>
+          <t>排名 {0}</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Time up</t>
+          <t>Rank {0}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.External</t>
+          <t>UI.Result.Reason.KillLimit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>异常结束</t>
+          <t>击杀达成</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ended externally</t>
+          <t>Kill limit reached</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>UI.Result.RecordsEmpty</t>
+          <t>UI.Result.Reason.TimeLimit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>暂无战绩</t>
+          <t>时间到</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No recent matches</t>
+          <t>Time up</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>UI.Settings.Volume</t>
+          <t>UI.Result.Reason.External</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>主音量</t>
+          <t>异常结束</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Master Volume</t>
+          <t>Ended externally</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>UI.Settings.Sound</t>
+          <t>UI.Result.RecordsEmpty</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>暂无战绩</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sound Effects</t>
+          <t>No recent matches</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality</t>
+          <t>UI.Settings.Volume</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>画质</t>
+          <t>主音量</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Master Volume</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.Low</t>
+          <t>UI.Settings.Sound</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>音效</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Sound Effects</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.Medium</t>
+          <t>UI.Settings.Quality</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>画质</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.High</t>
+          <t>UI.Settings.Quality.Low</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>UI.Settings.Language</t>
+          <t>UI.Settings.Quality.Medium</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>UI.Settings.Account</t>
+          <t>UI.Settings.Quality.High</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>账号 {0}</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Account {0}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>UI.Settings.Server</t>
+          <t>UI.Settings.Language</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>服务器 {0}</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Server {0}</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>UI.Settings.Language.Zh</t>
+          <t>UI.Settings.Account</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>账号 {0}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>Account {0}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
+          <t>UI.Settings.Server</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>服务器 {0}</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Server {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>UI.Settings.Language.Zh</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
           <t>UI.Settings.Language.En</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>English</t>
         </is>

--- a/Luban/Data/#ltext.xlsx
+++ b/Luban/Data/#ltext.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,644 +570,729 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>UI.Login.Title</t>
+          <t>Common.Confirm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>联机对战测试</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Online Playtest</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>UI.Login.Connecting</t>
+          <t>Common.Cancel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>连接中…</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Connecting…</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>UI.Login.Failed</t>
+          <t>UI.Login.Title</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>登录失败，请重试</t>
+          <t>联机对战测试</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sign-in failed, please retry</t>
+          <t>Online Playtest</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>UI.Login.GuestEnter</t>
+          <t>UI.Login.Connecting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>游客一键进入</t>
+          <t>连接中…</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Enter as Guest</t>
+          <t>Connecting…</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>UI.Login.NoServer</t>
+          <t>UI.Login.Failed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>未配置服务器地址（-meta.url）</t>
+          <t>登录失败，请重试</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Server address not configured (-meta.url)</t>
+          <t>Sign-in failed, please retry</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>UI.Lobby.RoomState</t>
+          <t>UI.Login.GuestEnter</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>人数 {0}/{1}</t>
+          <t>游客一键进入</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{0}/{1} players</t>
+          <t>Enter as Guest</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>UI.Lobby.QuickEnter</t>
+          <t>UI.Login.NoServer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>快速进入</t>
+          <t>未配置服务器地址（-meta.url）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Quick Join</t>
+          <t>Server address not configured (-meta.url)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>UI.Lobby.Records</t>
+          <t>UI.Lobby.RoomState</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>最近战绩</t>
+          <t>人数 {0}/{1}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Recent Matches</t>
+          <t>{0}/{1} players</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>UI.Lobby.Ready</t>
+          <t>UI.Lobby.QuickEnter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>就绪</t>
+          <t>快速进入</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Quick Join</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>UI.Lobby.Allocating</t>
+          <t>UI.Lobby.Records</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>分配房间中…</t>
+          <t>最近战绩</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Allocating room…</t>
+          <t>Recent Matches</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>UI.Lobby.EnterFailed</t>
+          <t>UI.Lobby.Ready</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>进入失败，请重试</t>
+          <t>就绪</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Join failed, please retry</t>
+          <t>Ready</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>UI.Lobby.RoomEmpty</t>
+          <t>UI.Lobby.Allocating</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>暂无房间</t>
+          <t>分配房间中…</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No rooms</t>
+          <t>Allocating room…</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>UI.Lobby.ListFailed</t>
+          <t>UI.Lobby.EnterFailed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>房间列表加载失败，请重试</t>
+          <t>进入失败，请重试</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Failed to load rooms, please retry</t>
+          <t>Join failed, please retry</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>UI.Room.Info</t>
+          <t>UI.Lobby.RoomEmpty</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>房间 {0}</t>
+          <t>暂无房间</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Room {0}</t>
+          <t>No rooms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>UI.Room.Waiting</t>
+          <t>UI.Lobby.ListFailed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>等待玩家 {0}/{1}</t>
+          <t>房间列表加载失败，请重试</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Waiting for players {0}/{1}</t>
+          <t>Failed to load rooms, please retry</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>UI.Room.PlayerState.Online</t>
+          <t>UI.Room.Info</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>房间 {0}</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Room {0}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>UI.Room.PlayerState.Connecting</t>
+          <t>UI.Room.Waiting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>连接中</t>
+          <t>等待玩家 {0}/{1}</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Connecting</t>
+          <t>Waiting for players {0}/{1}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>UI.Room.StartMatch</t>
+          <t>UI.Room.PlayerState.Online</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>开始对局</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Start Match</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>UI.Room.StartDenied</t>
+          <t>UI.Room.PlayerState.Connecting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>开局被拒：{0}</t>
+          <t>连接中</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Start denied: {0}</t>
+          <t>Connecting</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>UI.Result.Kills</t>
+          <t>UI.Room.StartMatch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>击杀 {0}</t>
+          <t>开始对局</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kills {0}</t>
+          <t>Start Match</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>UI.Result.Deaths</t>
+          <t>UI.Room.StartDenied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>死亡 {0}</t>
+          <t>开局被拒：{0}</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Deaths {0}</t>
+          <t>Start denied: {0}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>UI.Result.Score</t>
+          <t>UI.Result.Kills</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>比分 {0}</t>
+          <t>击杀 {0}</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Score {0}</t>
+          <t>Kills {0}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>UI.Result.Rank</t>
+          <t>UI.Result.Deaths</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>排名 {0}</t>
+          <t>死亡 {0}</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rank {0}</t>
+          <t>Deaths {0}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.KillLimit</t>
+          <t>UI.Result.Score</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>击杀达成</t>
+          <t>比分 {0}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Kill limit reached</t>
+          <t>Score {0}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.TimeLimit</t>
+          <t>UI.Result.Rank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>时间到</t>
+          <t>排名 {0}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Time up</t>
+          <t>Rank {0}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.External</t>
+          <t>UI.Result.Reason.KillLimit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>异常结束</t>
+          <t>击杀达成</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ended externally</t>
+          <t>Kill limit reached</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>UI.Result.RecordsEmpty</t>
+          <t>UI.Result.Reason.TimeLimit</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>暂无战绩</t>
+          <t>时间到</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No recent matches</t>
+          <t>Time up</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>UI.Settings.Volume</t>
+          <t>UI.Result.Reason.External</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>主音量</t>
+          <t>异常结束</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Master Volume</t>
+          <t>Ended externally</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>UI.Settings.Sound</t>
+          <t>UI.Result.RecordsEmpty</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>暂无战绩</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sound Effects</t>
+          <t>No recent matches</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality</t>
+          <t>UI.Settings.Volume</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>画质</t>
+          <t>主音量</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Master Volume</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.Low</t>
+          <t>UI.Settings.Sound</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>音效</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Sound Effects</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.Medium</t>
+          <t>UI.Settings.Quality</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>画质</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.High</t>
+          <t>UI.Settings.Quality.Low</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>UI.Settings.Language</t>
+          <t>UI.Settings.Quality.Medium</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>UI.Settings.Account</t>
+          <t>UI.Settings.Quality.High</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>账号 {0}</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Account {0}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>UI.Settings.Server</t>
+          <t>UI.Settings.Language</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>服务器 {0}</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Server {0}</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>UI.Settings.Language.Zh</t>
+          <t>UI.Settings.Account</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>账号 {0}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>Account {0}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
+          <t>UI.Settings.Server</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>服务器 {0}</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Server {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UI.Settings.Exit</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>退出对局</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Leave Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>UI.Settings.ExitConfirmTitle</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>退出对局</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Leave Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UI.Settings.ExitConfirmMessage</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>确定要退出当前对局吗？退出后将返回大厅。</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Leave the current match and return to the lobby?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>UI.Settings.Language.Zh</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
           <t>UI.Settings.Language.En</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>English</t>
         </is>

--- a/Luban/Data/#ltext.xlsx
+++ b/Luban/Data/#ltext.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,576 +723,627 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>UI.Lobby.Records</t>
+          <t>UI.Lobby.CreateRoom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>最近战绩</t>
+          <t>创建房间</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Recent Matches</t>
+          <t>Create Room</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>UI.Lobby.Ready</t>
+          <t>UI.Lobby.Creating</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>就绪</t>
+          <t>创建中…</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Creating…</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>UI.Lobby.Allocating</t>
+          <t>UI.Lobby.CreateFailed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>分配房间中…</t>
+          <t>创建房间失败</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Allocating room…</t>
+          <t>Create room failed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>UI.Lobby.EnterFailed</t>
+          <t>UI.Lobby.Records</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>进入失败，请重试</t>
+          <t>最近战绩</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Join failed, please retry</t>
+          <t>Recent Matches</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>UI.Lobby.RoomEmpty</t>
+          <t>UI.Lobby.Ready</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>暂无房间</t>
+          <t>就绪</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No rooms</t>
+          <t>Ready</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>UI.Lobby.ListFailed</t>
+          <t>UI.Lobby.Allocating</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>房间列表加载失败，请重试</t>
+          <t>分配房间中…</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Failed to load rooms, please retry</t>
+          <t>Allocating room…</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>UI.Room.Info</t>
+          <t>UI.Lobby.EnterFailed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>房间 {0}</t>
+          <t>进入失败，请重试</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Room {0}</t>
+          <t>Join failed, please retry</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>UI.Room.Waiting</t>
+          <t>UI.Lobby.RoomEmpty</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>等待玩家 {0}/{1}</t>
+          <t>暂无房间</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Waiting for players {0}/{1}</t>
+          <t>No rooms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>UI.Room.PlayerState.Online</t>
+          <t>UI.Lobby.ListFailed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>房间列表加载失败，请重试</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Failed to load rooms, please retry</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>UI.Room.PlayerState.Connecting</t>
+          <t>UI.Room.Info</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>连接中</t>
+          <t>房间 {0}</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Connecting</t>
+          <t>Room {0}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>UI.Room.StartMatch</t>
+          <t>UI.Room.Waiting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>开始对局</t>
+          <t>等待玩家 {0}/{1}</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Start Match</t>
+          <t>Waiting for players {0}/{1}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>UI.Room.StartDenied</t>
+          <t>UI.Room.PlayerState.Online</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>开局被拒：{0}</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Start denied: {0}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>UI.Result.Kills</t>
+          <t>UI.Room.PlayerState.Connecting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>击杀 {0}</t>
+          <t>连接中</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Kills {0}</t>
+          <t>Connecting</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>UI.Result.Deaths</t>
+          <t>UI.Room.StartMatch</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>死亡 {0}</t>
+          <t>开始对局</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deaths {0}</t>
+          <t>Start Match</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>UI.Result.Score</t>
+          <t>UI.Room.StartDenied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>比分 {0}</t>
+          <t>开局被拒：{0}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Score {0}</t>
+          <t>Start denied: {0}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>UI.Result.Rank</t>
+          <t>UI.Result.Kills</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>排名 {0}</t>
+          <t>击杀 {0}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Rank {0}</t>
+          <t>Kills {0}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.KillLimit</t>
+          <t>UI.Result.Deaths</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>击杀达成</t>
+          <t>死亡 {0}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Kill limit reached</t>
+          <t>Deaths {0}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.TimeLimit</t>
+          <t>UI.Result.Score</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>时间到</t>
+          <t>比分 {0}</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Time up</t>
+          <t>Score {0}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.External</t>
+          <t>UI.Result.Rank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>异常结束</t>
+          <t>排名 {0}</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ended externally</t>
+          <t>Rank {0}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>UI.Result.RecordsEmpty</t>
+          <t>UI.Result.Reason.KillLimit</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>暂无战绩</t>
+          <t>击杀达成</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>No recent matches</t>
+          <t>Kill limit reached</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>UI.Settings.Volume</t>
+          <t>UI.Result.Reason.TimeLimit</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>主音量</t>
+          <t>时间到</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Master Volume</t>
+          <t>Time up</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>UI.Settings.Sound</t>
+          <t>UI.Result.Reason.External</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>异常结束</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sound Effects</t>
+          <t>Ended externally</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality</t>
+          <t>UI.Result.RecordsEmpty</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>画质</t>
+          <t>暂无战绩</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>No recent matches</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.Low</t>
+          <t>UI.Settings.Volume</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>主音量</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Master Volume</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.Medium</t>
+          <t>UI.Settings.Sound</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>音效</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Sound Effects</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.High</t>
+          <t>UI.Settings.Quality</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>画质</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>UI.Settings.Language</t>
+          <t>UI.Settings.Quality.Low</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>低</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>UI.Settings.Account</t>
+          <t>UI.Settings.Quality.Medium</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>账号 {0}</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Account {0}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>UI.Settings.Server</t>
+          <t>UI.Settings.Quality.High</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>服务器 {0}</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Server {0}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>UI.Settings.Exit</t>
+          <t>UI.Settings.Language</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>退出对局</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Leave Match</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>UI.Settings.ExitConfirmTitle</t>
+          <t>UI.Settings.Account</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>退出对局</t>
+          <t>账号 {0}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Leave Match</t>
+          <t>Account {0}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>UI.Settings.ExitConfirmMessage</t>
+          <t>UI.Settings.Server</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>确定要退出当前对局吗？退出后将返回大厅。</t>
+          <t>服务器 {0}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Leave the current match and return to the lobby?</t>
+          <t>Server {0}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>UI.Settings.Language.Zh</t>
+          <t>UI.Settings.Exit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>退出对局</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>Leave Match</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
+          <t>UI.Settings.ExitConfirmTitle</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>退出对局</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Leave Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>UI.Settings.ExitConfirmMessage</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>确定要退出当前对局吗？退出后将返回大厅。</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Leave the current match and return to the lobby?</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>UI.Settings.Language.Zh</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
           <t>UI.Settings.Language.En</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>English</t>
         </is>

--- a/Luban/Data/#ltext.xlsx
+++ b/Luban/Data/#ltext.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,6 +1349,28 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>UI.Settings.ExitWorkbench</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>退出工作台</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Exit Workbench</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Luban/Data/#ltext.xlsx
+++ b/Luban/Data/#ltext.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,6 +1371,57 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>UI.Lobby.Map</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>地图</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>UI.Lobby.Players</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Players</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UI.Lobby.PlayersOption</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>{0} 人</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{0} players</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Luban/Data/#ltext.xlsx
+++ b/Luban/Data/#ltext.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,17 +1097,17 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>UI.Result.RecordsEmpty</t>
+          <t>UI.Result.NoMatchData</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>暂无战绩</t>
+          <t>暂无本局数据</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No recent matches</t>
+          <t>No match data</t>
         </is>
       </c>
     </row>
@@ -1419,6 +1419,23 @@
       <c r="D58" t="inlineStr">
         <is>
           <t>{0} players</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UI.Records.Empty</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>暂无战绩</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>No recent matches</t>
         </is>
       </c>
     </row>

--- a/Luban/Data/#ltext.xlsx
+++ b/Luban/Data/#ltext.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,836 +604,1227 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>UI.Login.Title</t>
+          <t>Common.On</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>联机对战测试</t>
+          <t>开</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Online Playtest</t>
+          <t>On</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>UI.Login.Connecting</t>
+          <t>Common.Off</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>连接中…</t>
+          <t>关</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Connecting…</t>
+          <t>Off</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>UI.Login.Failed</t>
+          <t>UI.Login.Title</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>登录失败，请重试</t>
+          <t>联机对战测试</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sign-in failed, please retry</t>
+          <t>Online Playtest</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>UI.Login.GuestEnter</t>
+          <t>UI.Login.Connecting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>游客一键进入</t>
+          <t>连接中…</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Enter as Guest</t>
+          <t>Connecting…</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>UI.Login.NoServer</t>
+          <t>UI.Login.Failed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>未配置服务器地址（-meta.url）</t>
+          <t>登录失败，请重试</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Server address not configured (-meta.url)</t>
+          <t>Sign-in failed, please retry</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>UI.Lobby.RoomState</t>
+          <t>UI.Login.GuestEnter</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>人数 {0}/{1}</t>
+          <t>游客一键进入</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{0}/{1} players</t>
+          <t>Enter as Guest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>UI.Lobby.QuickEnter</t>
+          <t>UI.Login.NoServer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>快速进入</t>
+          <t>未配置服务器地址（-meta.url）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Quick Join</t>
+          <t>Server address not configured (-meta.url)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>UI.Lobby.CreateRoom</t>
+          <t>UI.Lobby.RoomState</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>创建房间</t>
+          <t>人数 {0}/{1}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Create Room</t>
+          <t>{0}/{1} players</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>UI.Lobby.Creating</t>
+          <t>UI.Lobby.QuickEnter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>创建中…</t>
+          <t>快速进入</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Creating…</t>
+          <t>Quick Join</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>UI.Lobby.CreateFailed</t>
+          <t>UI.Lobby.CreateRoom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>创建房间失败</t>
+          <t>创建房间</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Create room failed</t>
+          <t>Create Room</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>UI.Lobby.Records</t>
+          <t>UI.Lobby.Creating</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>最近战绩</t>
+          <t>创建中…</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Recent Matches</t>
+          <t>Creating…</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>UI.Lobby.Ready</t>
+          <t>UI.Lobby.CreateFailed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>就绪</t>
+          <t>创建房间失败</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Create room failed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>UI.Lobby.Allocating</t>
+          <t>UI.Lobby.Records</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>分配房间中…</t>
+          <t>最近战绩</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Allocating room…</t>
+          <t>Recent Matches</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>UI.Lobby.EnterFailed</t>
+          <t>UI.Lobby.Ready</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>进入失败，请重试</t>
+          <t>就绪</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Join failed, please retry</t>
+          <t>Ready</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>UI.Lobby.RoomEmpty</t>
+          <t>UI.Lobby.Allocating</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>暂无房间</t>
+          <t>分配房间中…</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No rooms</t>
+          <t>Allocating room…</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>UI.Lobby.ListFailed</t>
+          <t>UI.Lobby.EnterFailed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>房间列表加载失败，请重试</t>
+          <t>进入失败，请重试</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Failed to load rooms, please retry</t>
+          <t>Join failed, please retry</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>UI.Room.Info</t>
+          <t>UI.Lobby.RoomEmpty</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>房间 {0}</t>
+          <t>暂无房间</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Room {0}</t>
+          <t>No rooms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>UI.Room.Waiting</t>
+          <t>UI.Lobby.ListFailed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>等待玩家 {0}/{1}</t>
+          <t>房间列表加载失败，请重试</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Waiting for players {0}/{1}</t>
+          <t>Failed to load rooms, please retry</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>UI.Room.PlayerState.Online</t>
+          <t>UI.Room.Info</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>房间 {0}</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Room {0}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>UI.Room.PlayerState.Connecting</t>
+          <t>UI.Room.Waiting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>连接中</t>
+          <t>等待玩家 {0}/{1}</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Connecting</t>
+          <t>Waiting for players {0}/{1}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>UI.Room.StartMatch</t>
+          <t>UI.Room.PlayerState.Online</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>开始对局</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Start Match</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>UI.Room.StartDenied</t>
+          <t>UI.Room.PlayerState.Connecting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>开局被拒：{0}</t>
+          <t>连接中</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Start denied: {0}</t>
+          <t>Connecting</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>UI.Result.Kills</t>
+          <t>UI.Room.StartMatch</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>击杀 {0}</t>
+          <t>开始对局</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Kills {0}</t>
+          <t>Start Match</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>UI.Result.Deaths</t>
+          <t>UI.Room.StartDenied</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>死亡 {0}</t>
+          <t>开局被拒：{0}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Deaths {0}</t>
+          <t>Start denied: {0}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>UI.Result.Score</t>
+          <t>UI.Result.Kills</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>比分 {0}</t>
+          <t>击杀 {0}</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Score {0}</t>
+          <t>Kills {0}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>UI.Result.Rank</t>
+          <t>UI.Result.Deaths</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>排名 {0}</t>
+          <t>死亡 {0}</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Rank {0}</t>
+          <t>Deaths {0}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.KillLimit</t>
+          <t>UI.Result.Score</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>击杀达成</t>
+          <t>比分 {0}</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kill limit reached</t>
+          <t>Score {0}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.TimeLimit</t>
+          <t>UI.Result.Rank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>时间到</t>
+          <t>排名 {0}</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Time up</t>
+          <t>Rank {0}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>UI.Result.Reason.External</t>
+          <t>UI.Result.Reason.KillLimit</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>异常结束</t>
+          <t>击杀达成</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ended externally</t>
+          <t>Kill limit reached</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>UI.Result.NoMatchData</t>
+          <t>UI.Result.Reason.TimeLimit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>暂无本局数据</t>
+          <t>时间到</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No match data</t>
+          <t>Time up</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>UI.Settings.Volume</t>
+          <t>UI.Result.Reason.External</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>主音量</t>
+          <t>异常结束</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Master Volume</t>
+          <t>Ended externally</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>UI.Settings.Sound</t>
+          <t>UI.Result.NoMatchData</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>暂无本局数据</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sound Effects</t>
+          <t>No match data</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality</t>
+          <t>UI.Settings.Volume</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>画质</t>
+          <t>主音量</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Master Volume</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.Low</t>
+          <t>UI.Settings.Sound</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>音效</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Sound Effects</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.Medium</t>
+          <t>UI.Settings.Quality</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>画质</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>UI.Settings.Quality.High</t>
+          <t>UI.Settings.Quality.Low</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>UI.Settings.Language</t>
+          <t>UI.Settings.Quality.Medium</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>UI.Settings.Account</t>
+          <t>UI.Settings.Quality.High</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>账号 {0}</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Account {0}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>UI.Settings.Server</t>
+          <t>UI.Settings.Language</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>服务器 {0}</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Server {0}</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>UI.Settings.Exit</t>
+          <t>UI.Settings.Account</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>退出对局</t>
+          <t>账号 {0}</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Leave Match</t>
+          <t>Account {0}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>UI.Settings.ExitConfirmTitle</t>
+          <t>UI.Settings.Server</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>退出对局</t>
+          <t>服务器 {0}</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Leave Match</t>
+          <t>Server {0}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>UI.Settings.ExitConfirmMessage</t>
+          <t>UI.Settings.Exit</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>确定要退出当前对局吗？退出后将返回大厅。</t>
+          <t>退出对局</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Leave the current match and return to the lobby?</t>
+          <t>Leave Match</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>UI.Settings.Language.Zh</t>
+          <t>UI.Settings.ExitConfirmTitle</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>退出对局</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>Leave Match</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>UI.Settings.Language.En</t>
+          <t>UI.Settings.ExitConfirmMessage</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>确定要退出当前对局吗？退出后将返回大厅。</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Leave the current match and return to the lobby?</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UI.Settings.ExitWorkbench</t>
+          <t>UI.Settings.Language.Zh</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>退出工作台</t>
+          <t>简体中文</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Exit Workbench</t>
+          <t>简体中文</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>UI.Lobby.Map</t>
+          <t>UI.Settings.Language.En</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>地图</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>UI.Lobby.Players</t>
+          <t>UI.Settings.ExitWorkbench</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>退出工作台</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Players</t>
+          <t>Exit Workbench</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>UI.Lobby.PlayersOption</t>
+          <t>UI.Settings.Tab.Audio</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{0} 人</t>
+          <t>音频</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{0} players</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
+          <t>UI.Settings.Tab.Graphics</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>图形</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Graphics</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UI.Settings.Tab.Display</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>显示</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UI.Settings.Tab.Control</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>控制</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>UI.Settings.Tab.General</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UI.Settings.DisplayMode</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>显示模式</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Display Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UI.Settings.DisplayMode.Fullscreen</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>独占全屏</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Exclusive Fullscreen</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>UI.Settings.DisplayMode.Borderless</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>无边框窗口</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Borderless</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>UI.Settings.DisplayMode.Windowed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>窗口</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Windowed</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UI.Settings.Resolution</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>分辨率</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UI.Settings.Resolution.FollowDisplay</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>跟随显示器</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Follow Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UI.Settings.FrameRate</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>帧率上限</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Frame Rate Limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>UI.Settings.FrameRate.Unlimited</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>无限制</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UI.Settings.VSync</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>垂直同步</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>V-Sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>UI.Settings.FollowPreset</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>跟随画质预设</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Follow Preset</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>UI.Settings.LookSensitivity</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>视角灵敏度</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Look Sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UI.Settings.AdsSensitivity</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>开镜灵敏度</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ADS Sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>UI.Settings.InvertLookY</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>垂直视角反转</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Invert Look Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UI.Settings.ResetDefaults</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Reset to Defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>UI.Settings.ResetConfirmTitle</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>恢复默认设置</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Reset Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>UI.Settings.ResetConfirmMessage</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>所有设置将恢复为默认值，确定继续吗？</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Restore all settings to their defaults?</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>UI.Lobby.Map</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>地图</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>UI.Lobby.Players</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Players</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>UI.Lobby.PlayersOption</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>{0} 人</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{0} players</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
           <t>UI.Records.Empty</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>暂无战绩</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>No recent matches</t>
         </is>
